--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_BLACK_BEAR.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_BLACK_BEAR.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O109"/>
+  <dimension ref="A1:P109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -537,6 +537,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -605,10 +606,15 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -661,7 +667,8 @@
       </c>
       <c r="M4" s="4" t="inlineStr"/>
       <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -710,7 +717,8 @@
       </c>
       <c r="M5" s="6" t="inlineStr"/>
       <c r="N5" s="6" t="inlineStr"/>
-      <c r="O5" s="6" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -763,7 +771,8 @@
       </c>
       <c r="M6" s="4" t="inlineStr"/>
       <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -824,7 +833,8 @@
       </c>
       <c r="M7" s="6" t="inlineStr"/>
       <c r="N7" s="6" t="inlineStr"/>
-      <c r="O7" s="6" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -884,8 +894,13 @@
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
-      <c r="O8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -945,8 +960,13 @@
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr"/>
-      <c r="O9" s="6" t="inlineStr"/>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -1007,7 +1027,8 @@
       </c>
       <c r="M10" s="4" t="inlineStr"/>
       <c r="N10" s="4" t="inlineStr"/>
-      <c r="O10" s="4" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -1067,8 +1088,13 @@
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr"/>
-      <c r="N11" s="6" t="inlineStr"/>
-      <c r="O11" s="6" t="inlineStr"/>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -1128,8 +1154,13 @@
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr"/>
-      <c r="O12" s="4" t="inlineStr"/>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -1190,7 +1221,8 @@
       </c>
       <c r="M13" s="6" t="inlineStr"/>
       <c r="N13" s="6" t="inlineStr"/>
-      <c r="O13" s="6" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -1250,8 +1282,13 @@
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1311,8 +1348,13 @@
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr"/>
-      <c r="N15" s="6" t="inlineStr"/>
-      <c r="O15" s="6" t="inlineStr"/>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -1365,7 +1407,8 @@
       </c>
       <c r="M16" s="4" t="inlineStr"/>
       <c r="N16" s="4" t="inlineStr"/>
-      <c r="O16" s="4" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -1425,8 +1468,13 @@
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr"/>
-      <c r="N17" s="6" t="inlineStr"/>
-      <c r="O17" s="6" t="inlineStr"/>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -1486,8 +1534,13 @@
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr"/>
-      <c r="O18" s="4" t="inlineStr"/>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" s="4" t="inlineStr"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -1547,8 +1600,13 @@
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr"/>
-      <c r="N19" s="6" t="inlineStr"/>
-      <c r="O19" s="6" t="inlineStr"/>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
@@ -1608,8 +1666,13 @@
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr"/>
-      <c r="O20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="4" t="inlineStr"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -1669,8 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr"/>
-      <c r="N21" s="6" t="inlineStr"/>
-      <c r="O21" s="6" t="inlineStr"/>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
@@ -1730,8 +1798,13 @@
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr"/>
-      <c r="N22" s="4" t="inlineStr"/>
-      <c r="O22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="4" t="inlineStr"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -1791,8 +1864,13 @@
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="6" t="inlineStr"/>
-      <c r="O23" s="6" t="inlineStr"/>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="6" t="inlineStr"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
@@ -1852,8 +1930,13 @@
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr"/>
-      <c r="O24" s="4" t="inlineStr"/>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" s="4" t="inlineStr"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -1913,8 +1996,13 @@
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr"/>
-      <c r="N25" s="6" t="inlineStr"/>
-      <c r="O25" s="6" t="inlineStr"/>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="6" t="inlineStr"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -1974,8 +2062,13 @@
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr"/>
-      <c r="O26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" s="4" t="inlineStr"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
@@ -2035,8 +2128,13 @@
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr"/>
-      <c r="N27" s="6" t="inlineStr"/>
-      <c r="O27" s="6" t="inlineStr"/>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" s="6" t="inlineStr"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
@@ -2096,8 +2194,13 @@
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr"/>
-      <c r="N28" s="4" t="inlineStr"/>
-      <c r="O28" s="4" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" s="4" t="inlineStr"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
@@ -2157,8 +2260,13 @@
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr"/>
-      <c r="N29" s="6" t="inlineStr"/>
-      <c r="O29" s="6" t="inlineStr"/>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" s="6" t="inlineStr"/>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
@@ -2218,8 +2326,13 @@
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr"/>
-      <c r="N30" s="4" t="inlineStr"/>
-      <c r="O30" s="4" t="inlineStr"/>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" s="4" t="inlineStr"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
@@ -2279,8 +2392,13 @@
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr"/>
-      <c r="N31" s="6" t="inlineStr"/>
-      <c r="O31" s="6" t="inlineStr"/>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" s="6" t="inlineStr"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
@@ -2340,8 +2458,13 @@
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr"/>
-      <c r="N32" s="4" t="inlineStr"/>
-      <c r="O32" s="4" t="inlineStr"/>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" s="4" t="inlineStr"/>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -2401,8 +2524,13 @@
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr"/>
-      <c r="N33" s="6" t="inlineStr"/>
-      <c r="O33" s="6" t="inlineStr"/>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" s="6" t="inlineStr"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
@@ -2463,7 +2591,8 @@
       </c>
       <c r="M34" s="4" t="inlineStr"/>
       <c r="N34" s="4" t="inlineStr"/>
-      <c r="O34" s="4" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" s="4" t="inlineStr"/>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
@@ -2523,8 +2652,13 @@
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr"/>
-      <c r="N35" s="6" t="inlineStr"/>
-      <c r="O35" s="6" t="inlineStr"/>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" s="6" t="inlineStr"/>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
@@ -2584,8 +2718,13 @@
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr"/>
-      <c r="N36" s="4" t="inlineStr"/>
-      <c r="O36" s="4" t="inlineStr"/>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" s="4" t="inlineStr"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -2645,8 +2784,13 @@
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr"/>
-      <c r="N37" s="6" t="inlineStr"/>
-      <c r="O37" s="6" t="inlineStr"/>
+      <c r="N37" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" s="6" t="inlineStr"/>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
@@ -2706,8 +2850,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr"/>
-      <c r="N38" s="4" t="inlineStr"/>
-      <c r="O38" s="4" t="inlineStr"/>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" s="4" t="inlineStr"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
@@ -2767,8 +2916,13 @@
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr"/>
-      <c r="N39" s="6" t="inlineStr"/>
-      <c r="O39" s="6" t="inlineStr"/>
+      <c r="N39" s="6" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" s="6" t="inlineStr"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
@@ -2828,8 +2982,13 @@
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr"/>
-      <c r="N40" s="4" t="inlineStr"/>
-      <c r="O40" s="4" t="inlineStr"/>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" s="4" t="inlineStr"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
@@ -2889,8 +3048,13 @@
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr"/>
-      <c r="N41" s="6" t="inlineStr"/>
-      <c r="O41" s="6" t="inlineStr"/>
+      <c r="N41" s="6" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" s="6" t="inlineStr"/>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
@@ -2950,8 +3114,13 @@
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr"/>
-      <c r="N42" s="4" t="inlineStr"/>
-      <c r="O42" s="4" t="inlineStr"/>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" s="4" t="inlineStr"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -3011,8 +3180,13 @@
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr"/>
-      <c r="N43" s="6" t="inlineStr"/>
-      <c r="O43" s="6" t="inlineStr"/>
+      <c r="N43" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" s="6" t="inlineStr"/>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
@@ -3072,8 +3246,13 @@
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr"/>
-      <c r="N44" s="4" t="inlineStr"/>
-      <c r="O44" s="4" t="inlineStr"/>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" s="4" t="inlineStr"/>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
@@ -3133,8 +3312,13 @@
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr"/>
-      <c r="N45" s="6" t="inlineStr"/>
-      <c r="O45" s="6" t="inlineStr"/>
+      <c r="N45" s="6" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" s="6" t="inlineStr"/>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
@@ -3194,8 +3378,13 @@
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr"/>
-      <c r="N46" s="4" t="inlineStr"/>
-      <c r="O46" s="4" t="inlineStr"/>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" s="4" t="inlineStr"/>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
@@ -3255,8 +3444,13 @@
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr"/>
-      <c r="N47" s="6" t="inlineStr"/>
-      <c r="O47" s="6" t="inlineStr"/>
+      <c r="N47" s="6" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" s="6" t="inlineStr"/>
     </row>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
@@ -3316,8 +3510,13 @@
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr"/>
-      <c r="N48" s="4" t="inlineStr"/>
-      <c r="O48" s="4" t="inlineStr"/>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" s="4" t="inlineStr"/>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
@@ -3377,8 +3576,13 @@
         </is>
       </c>
       <c r="M49" s="6" t="inlineStr"/>
-      <c r="N49" s="6" t="inlineStr"/>
-      <c r="O49" s="6" t="inlineStr"/>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" s="6" t="inlineStr"/>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
@@ -3438,8 +3642,13 @@
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr"/>
-      <c r="N50" s="4" t="inlineStr"/>
-      <c r="O50" s="4" t="inlineStr"/>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" s="4" t="inlineStr"/>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
@@ -3499,8 +3708,13 @@
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr"/>
-      <c r="N51" s="6" t="inlineStr"/>
-      <c r="O51" s="6" t="inlineStr"/>
+      <c r="N51" s="6" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" s="6" t="inlineStr"/>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
@@ -3560,8 +3774,13 @@
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr"/>
-      <c r="N52" s="4" t="inlineStr"/>
-      <c r="O52" s="4" t="inlineStr"/>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" s="4" t="inlineStr"/>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
@@ -3621,8 +3840,13 @@
         </is>
       </c>
       <c r="M53" s="6" t="inlineStr"/>
-      <c r="N53" s="6" t="inlineStr"/>
-      <c r="O53" s="6" t="inlineStr"/>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" s="6" t="inlineStr"/>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
@@ -3682,8 +3906,13 @@
         </is>
       </c>
       <c r="M54" s="4" t="inlineStr"/>
-      <c r="N54" s="4" t="inlineStr"/>
-      <c r="O54" s="4" t="inlineStr"/>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" s="4" t="inlineStr"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
@@ -3743,8 +3972,13 @@
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr"/>
-      <c r="N55" s="6" t="inlineStr"/>
-      <c r="O55" s="6" t="inlineStr"/>
+      <c r="N55" s="6" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" s="6" t="inlineStr"/>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
@@ -3804,8 +4038,13 @@
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr"/>
-      <c r="N56" s="4" t="inlineStr"/>
-      <c r="O56" s="4" t="inlineStr"/>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" s="4" t="inlineStr"/>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
@@ -3865,8 +4104,13 @@
         </is>
       </c>
       <c r="M57" s="6" t="inlineStr"/>
-      <c r="N57" s="6" t="inlineStr"/>
-      <c r="O57" s="6" t="inlineStr"/>
+      <c r="N57" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" s="6" t="inlineStr"/>
     </row>
     <row r="58" ht="24" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
@@ -3926,8 +4170,13 @@
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr"/>
-      <c r="N58" s="4" t="inlineStr"/>
-      <c r="O58" s="4" t="inlineStr"/>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" s="4" t="inlineStr"/>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
@@ -3988,7 +4237,8 @@
       </c>
       <c r="M59" s="6" t="inlineStr"/>
       <c r="N59" s="6" t="inlineStr"/>
-      <c r="O59" s="6" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" s="6" t="inlineStr"/>
     </row>
     <row r="60" ht="24" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
@@ -4048,8 +4298,13 @@
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr"/>
-      <c r="N60" s="4" t="inlineStr"/>
-      <c r="O60" s="4" t="inlineStr"/>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" s="4" t="inlineStr"/>
     </row>
     <row r="61" ht="32" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
@@ -4109,8 +4364,13 @@
         </is>
       </c>
       <c r="M61" s="6" t="inlineStr"/>
-      <c r="N61" s="6" t="inlineStr"/>
-      <c r="O61" s="6" t="inlineStr"/>
+      <c r="N61" s="6" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" s="6" t="inlineStr"/>
     </row>
     <row r="62" ht="32" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
@@ -4170,8 +4430,13 @@
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr"/>
-      <c r="N62" s="4" t="inlineStr"/>
-      <c r="O62" s="4" t="inlineStr"/>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" s="4" t="inlineStr"/>
     </row>
     <row r="63" ht="32" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
@@ -4231,8 +4496,13 @@
         </is>
       </c>
       <c r="M63" s="6" t="inlineStr"/>
-      <c r="N63" s="6" t="inlineStr"/>
-      <c r="O63" s="6" t="inlineStr"/>
+      <c r="N63" s="6" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" s="6" t="inlineStr"/>
     </row>
     <row r="64" ht="32" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
@@ -4292,8 +4562,13 @@
         </is>
       </c>
       <c r="M64" s="4" t="inlineStr"/>
-      <c r="N64" s="4" t="inlineStr"/>
-      <c r="O64" s="4" t="inlineStr"/>
+      <c r="N64" s="4" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" s="4" t="inlineStr"/>
     </row>
     <row r="65" ht="32" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
@@ -4353,8 +4628,13 @@
         </is>
       </c>
       <c r="M65" s="6" t="inlineStr"/>
-      <c r="N65" s="6" t="inlineStr"/>
-      <c r="O65" s="6" t="inlineStr"/>
+      <c r="N65" s="6" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" s="6" t="inlineStr"/>
     </row>
     <row r="66" ht="32" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
@@ -4414,8 +4694,13 @@
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr"/>
-      <c r="N66" s="4" t="inlineStr"/>
-      <c r="O66" s="4" t="inlineStr"/>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" s="4" t="inlineStr"/>
     </row>
     <row r="67" ht="32" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
@@ -4475,8 +4760,13 @@
         </is>
       </c>
       <c r="M67" s="6" t="inlineStr"/>
-      <c r="N67" s="6" t="inlineStr"/>
-      <c r="O67" s="6" t="inlineStr"/>
+      <c r="N67" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" s="6" t="inlineStr"/>
     </row>
     <row r="68" ht="32" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
@@ -4536,8 +4826,13 @@
         </is>
       </c>
       <c r="M68" s="4" t="inlineStr"/>
-      <c r="N68" s="4" t="inlineStr"/>
-      <c r="O68" s="4" t="inlineStr"/>
+      <c r="N68" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" s="4" t="inlineStr"/>
     </row>
     <row r="69" ht="32" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
@@ -4597,8 +4892,13 @@
         </is>
       </c>
       <c r="M69" s="6" t="inlineStr"/>
-      <c r="N69" s="6" t="inlineStr"/>
-      <c r="O69" s="6" t="inlineStr"/>
+      <c r="N69" s="6" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" s="6" t="inlineStr"/>
     </row>
     <row r="70" ht="32" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
@@ -4658,8 +4958,13 @@
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr"/>
-      <c r="N70" s="4" t="inlineStr"/>
-      <c r="O70" s="4" t="inlineStr"/>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" s="4" t="inlineStr"/>
     </row>
     <row r="71" ht="32" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
@@ -4719,8 +5024,13 @@
         </is>
       </c>
       <c r="M71" s="6" t="inlineStr"/>
-      <c r="N71" s="6" t="inlineStr"/>
-      <c r="O71" s="6" t="inlineStr"/>
+      <c r="N71" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" s="6" t="inlineStr"/>
     </row>
     <row r="72" ht="32" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
@@ -4780,8 +5090,13 @@
         </is>
       </c>
       <c r="M72" s="4" t="inlineStr"/>
-      <c r="N72" s="4" t="inlineStr"/>
-      <c r="O72" s="4" t="inlineStr"/>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" s="4" t="inlineStr"/>
     </row>
     <row r="73" ht="32" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
@@ -4841,8 +5156,13 @@
         </is>
       </c>
       <c r="M73" s="6" t="inlineStr"/>
-      <c r="N73" s="6" t="inlineStr"/>
-      <c r="O73" s="6" t="inlineStr"/>
+      <c r="N73" s="6" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" s="6" t="inlineStr"/>
     </row>
     <row r="74" ht="32" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
@@ -4902,8 +5222,13 @@
         </is>
       </c>
       <c r="M74" s="4" t="inlineStr"/>
-      <c r="N74" s="4" t="inlineStr"/>
-      <c r="O74" s="4" t="inlineStr"/>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" s="4" t="inlineStr"/>
     </row>
     <row r="75" ht="32" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
@@ -4963,8 +5288,13 @@
         </is>
       </c>
       <c r="M75" s="6" t="inlineStr"/>
-      <c r="N75" s="6" t="inlineStr"/>
-      <c r="O75" s="6" t="inlineStr"/>
+      <c r="N75" s="6" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" s="6" t="inlineStr"/>
     </row>
     <row r="76" ht="32" customHeight="1">
       <c r="A76" s="3" t="inlineStr">
@@ -5024,8 +5354,13 @@
         </is>
       </c>
       <c r="M76" s="4" t="inlineStr"/>
-      <c r="N76" s="4" t="inlineStr"/>
-      <c r="O76" s="4" t="inlineStr"/>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" s="4" t="inlineStr"/>
     </row>
     <row r="77" ht="32" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
@@ -5085,8 +5420,13 @@
         </is>
       </c>
       <c r="M77" s="6" t="inlineStr"/>
-      <c r="N77" s="6" t="inlineStr"/>
-      <c r="O77" s="6" t="inlineStr"/>
+      <c r="N77" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" s="6" t="inlineStr"/>
     </row>
     <row r="78" ht="32" customHeight="1">
       <c r="A78" s="3" t="inlineStr">
@@ -5146,8 +5486,13 @@
         </is>
       </c>
       <c r="M78" s="4" t="inlineStr"/>
-      <c r="N78" s="4" t="inlineStr"/>
-      <c r="O78" s="4" t="inlineStr"/>
+      <c r="N78" s="4" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" s="4" t="inlineStr"/>
     </row>
     <row r="79" ht="24" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
@@ -5207,8 +5552,13 @@
         </is>
       </c>
       <c r="M79" s="6" t="inlineStr"/>
-      <c r="N79" s="6" t="inlineStr"/>
-      <c r="O79" s="6" t="inlineStr"/>
+      <c r="N79" s="6" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" s="6" t="inlineStr"/>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="3" t="inlineStr">
@@ -5268,8 +5618,13 @@
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr"/>
-      <c r="N80" s="4" t="inlineStr"/>
-      <c r="O80" s="4" t="inlineStr"/>
+      <c r="N80" s="4" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" s="4" t="inlineStr"/>
     </row>
     <row r="81" ht="32" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
@@ -5329,8 +5684,13 @@
         </is>
       </c>
       <c r="M81" s="6" t="inlineStr"/>
-      <c r="N81" s="6" t="inlineStr"/>
-      <c r="O81" s="6" t="inlineStr"/>
+      <c r="N81" s="6" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" s="6" t="inlineStr"/>
     </row>
     <row r="82" ht="32" customHeight="1">
       <c r="A82" s="3" t="inlineStr">
@@ -5390,8 +5750,13 @@
         </is>
       </c>
       <c r="M82" s="4" t="inlineStr"/>
-      <c r="N82" s="4" t="inlineStr"/>
-      <c r="O82" s="4" t="inlineStr"/>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" s="4" t="inlineStr"/>
     </row>
     <row r="83" ht="32" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
@@ -5451,8 +5816,13 @@
         </is>
       </c>
       <c r="M83" s="6" t="inlineStr"/>
-      <c r="N83" s="6" t="inlineStr"/>
-      <c r="O83" s="6" t="inlineStr"/>
+      <c r="N83" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" s="6" t="inlineStr"/>
     </row>
     <row r="84" ht="32" customHeight="1">
       <c r="A84" s="3" t="inlineStr">
@@ -5513,7 +5883,8 @@
       </c>
       <c r="M84" s="4" t="inlineStr"/>
       <c r="N84" s="4" t="inlineStr"/>
-      <c r="O84" s="4" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" s="4" t="inlineStr"/>
     </row>
     <row r="85" ht="32" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
@@ -5573,8 +5944,13 @@
         </is>
       </c>
       <c r="M85" s="6" t="inlineStr"/>
-      <c r="N85" s="6" t="inlineStr"/>
-      <c r="O85" s="6" t="inlineStr"/>
+      <c r="N85" s="6" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" s="6" t="inlineStr"/>
     </row>
     <row r="86" ht="48" customHeight="1">
       <c r="A86" s="3" t="inlineStr">
@@ -5634,8 +6010,13 @@
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr"/>
-      <c r="N86" s="4" t="inlineStr"/>
-      <c r="O86" s="4" t="inlineStr"/>
+      <c r="N86" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" s="4" t="inlineStr"/>
     </row>
     <row r="87" ht="32" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
@@ -5695,8 +6076,13 @@
         </is>
       </c>
       <c r="M87" s="6" t="inlineStr"/>
-      <c r="N87" s="6" t="inlineStr"/>
-      <c r="O87" s="6" t="inlineStr"/>
+      <c r="N87" s="6" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" s="6" t="inlineStr"/>
     </row>
     <row r="88" ht="48" customHeight="1">
       <c r="A88" s="3" t="inlineStr">
@@ -5756,8 +6142,13 @@
         </is>
       </c>
       <c r="M88" s="4" t="inlineStr"/>
-      <c r="N88" s="4" t="inlineStr"/>
-      <c r="O88" s="4" t="inlineStr"/>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" s="4" t="inlineStr"/>
     </row>
     <row r="89" ht="48" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
@@ -5817,8 +6208,13 @@
         </is>
       </c>
       <c r="M89" s="6" t="inlineStr"/>
-      <c r="N89" s="6" t="inlineStr"/>
-      <c r="O89" s="6" t="inlineStr"/>
+      <c r="N89" s="6" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" s="6" t="inlineStr"/>
     </row>
     <row r="90" ht="48" customHeight="1">
       <c r="A90" s="3" t="inlineStr">
@@ -5878,8 +6274,13 @@
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr"/>
-      <c r="N90" s="4" t="inlineStr"/>
-      <c r="O90" s="4" t="inlineStr"/>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" s="4" t="inlineStr"/>
     </row>
     <row r="91" ht="48" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
@@ -5927,8 +6328,13 @@
         </is>
       </c>
       <c r="M91" s="6" t="inlineStr"/>
-      <c r="N91" s="6" t="inlineStr"/>
-      <c r="O91" s="6" t="inlineStr"/>
+      <c r="N91" s="6" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" s="6" t="inlineStr"/>
     </row>
     <row r="92" ht="48" customHeight="1">
       <c r="A92" s="3" t="inlineStr">
@@ -5988,8 +6394,13 @@
         </is>
       </c>
       <c r="M92" s="4" t="inlineStr"/>
-      <c r="N92" s="4" t="inlineStr"/>
-      <c r="O92" s="4" t="inlineStr"/>
+      <c r="N92" s="4" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" s="4" t="inlineStr"/>
     </row>
     <row r="93" ht="48" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
@@ -6049,8 +6460,13 @@
         </is>
       </c>
       <c r="M93" s="6" t="inlineStr"/>
-      <c r="N93" s="6" t="inlineStr"/>
-      <c r="O93" s="6" t="inlineStr"/>
+      <c r="N93" s="6" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" s="6" t="inlineStr"/>
     </row>
     <row r="94" ht="48" customHeight="1">
       <c r="A94" s="3" t="inlineStr">
@@ -6110,8 +6526,13 @@
         </is>
       </c>
       <c r="M94" s="4" t="inlineStr"/>
-      <c r="N94" s="4" t="inlineStr"/>
-      <c r="O94" s="4" t="inlineStr"/>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" s="4" t="inlineStr"/>
     </row>
     <row r="95" ht="48" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
@@ -6171,8 +6592,13 @@
         </is>
       </c>
       <c r="M95" s="6" t="inlineStr"/>
-      <c r="N95" s="6" t="inlineStr"/>
-      <c r="O95" s="6" t="inlineStr"/>
+      <c r="N95" s="6" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" s="6" t="inlineStr"/>
     </row>
     <row r="96" ht="48" customHeight="1">
       <c r="A96" s="3" t="inlineStr">
@@ -6232,8 +6658,13 @@
         </is>
       </c>
       <c r="M96" s="4" t="inlineStr"/>
-      <c r="N96" s="4" t="inlineStr"/>
-      <c r="O96" s="4" t="inlineStr"/>
+      <c r="N96" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" s="4" t="inlineStr"/>
     </row>
     <row r="97" ht="48" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
@@ -6293,8 +6724,13 @@
         </is>
       </c>
       <c r="M97" s="6" t="inlineStr"/>
-      <c r="N97" s="6" t="inlineStr"/>
-      <c r="O97" s="6" t="inlineStr"/>
+      <c r="N97" s="6" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" s="6" t="inlineStr"/>
     </row>
     <row r="98" ht="48" customHeight="1">
       <c r="A98" s="3" t="inlineStr">
@@ -6354,8 +6790,13 @@
         </is>
       </c>
       <c r="M98" s="4" t="inlineStr"/>
-      <c r="N98" s="4" t="inlineStr"/>
-      <c r="O98" s="4" t="inlineStr"/>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" s="4" t="inlineStr"/>
     </row>
     <row r="99" ht="48" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
@@ -6415,8 +6856,13 @@
         </is>
       </c>
       <c r="M99" s="6" t="inlineStr"/>
-      <c r="N99" s="6" t="inlineStr"/>
-      <c r="O99" s="6" t="inlineStr"/>
+      <c r="N99" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" s="6" t="inlineStr"/>
     </row>
     <row r="100" ht="48" customHeight="1">
       <c r="A100" s="3" t="inlineStr">
@@ -6476,8 +6922,13 @@
         </is>
       </c>
       <c r="M100" s="4" t="inlineStr"/>
-      <c r="N100" s="4" t="inlineStr"/>
-      <c r="O100" s="4" t="inlineStr"/>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" s="4" t="inlineStr"/>
     </row>
     <row r="101" ht="48" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
@@ -6537,8 +6988,13 @@
         </is>
       </c>
       <c r="M101" s="6" t="inlineStr"/>
-      <c r="N101" s="6" t="inlineStr"/>
-      <c r="O101" s="6" t="inlineStr"/>
+      <c r="N101" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" s="6" t="inlineStr"/>
     </row>
     <row r="102" ht="48" customHeight="1">
       <c r="A102" s="3" t="inlineStr">
@@ -6598,8 +7054,13 @@
         </is>
       </c>
       <c r="M102" s="4" t="inlineStr"/>
-      <c r="N102" s="4" t="inlineStr"/>
-      <c r="O102" s="4" t="inlineStr"/>
+      <c r="N102" s="4" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" s="4" t="inlineStr"/>
     </row>
     <row r="103" ht="48" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
@@ -6659,8 +7120,13 @@
         </is>
       </c>
       <c r="M103" s="6" t="inlineStr"/>
-      <c r="N103" s="6" t="inlineStr"/>
-      <c r="O103" s="6" t="inlineStr"/>
+      <c r="N103" s="6" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" s="6" t="inlineStr"/>
     </row>
     <row r="104" ht="48" customHeight="1">
       <c r="A104" s="3" t="inlineStr">
@@ -6720,8 +7186,13 @@
         </is>
       </c>
       <c r="M104" s="4" t="inlineStr"/>
-      <c r="N104" s="4" t="inlineStr"/>
-      <c r="O104" s="4" t="inlineStr"/>
+      <c r="N104" s="4" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" s="4" t="inlineStr"/>
     </row>
     <row r="105" ht="48" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
@@ -6781,8 +7252,13 @@
         </is>
       </c>
       <c r="M105" s="6" t="inlineStr"/>
-      <c r="N105" s="6" t="inlineStr"/>
-      <c r="O105" s="6" t="inlineStr"/>
+      <c r="N105" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" s="6" t="inlineStr"/>
     </row>
     <row r="106" ht="48" customHeight="1">
       <c r="A106" s="3" t="inlineStr">
@@ -6842,8 +7318,13 @@
         </is>
       </c>
       <c r="M106" s="4" t="inlineStr"/>
-      <c r="N106" s="4" t="inlineStr"/>
-      <c r="O106" s="4" t="inlineStr"/>
+      <c r="N106" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" s="4" t="inlineStr"/>
     </row>
     <row r="107" ht="54" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
@@ -6891,8 +7372,13 @@
         </is>
       </c>
       <c r="M107" s="6" t="inlineStr"/>
-      <c r="N107" s="6" t="inlineStr"/>
-      <c r="O107" s="6" t="inlineStr"/>
+      <c r="N107" s="6" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" s="6" t="inlineStr"/>
     </row>
     <row r="108" ht="48" customHeight="1">
       <c r="A108" s="3" t="inlineStr">
@@ -6952,8 +7438,13 @@
         </is>
       </c>
       <c r="M108" s="4" t="inlineStr"/>
-      <c r="N108" s="4" t="inlineStr"/>
-      <c r="O108" s="4" t="inlineStr"/>
+      <c r="N108" s="4" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" s="4" t="inlineStr"/>
     </row>
     <row r="109" ht="48" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
@@ -7013,8 +7504,13 @@
         </is>
       </c>
       <c r="M109" s="6" t="inlineStr"/>
-      <c r="N109" s="6" t="inlineStr"/>
-      <c r="O109" s="6" t="inlineStr"/>
+      <c r="N109" s="6" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:O109"/>
